--- a/assets/infobasica/planilhas/aula26_nivel2.xlsx
+++ b/assets/infobasica/planilhas/aula26_nivel2.xlsx
@@ -535,9 +535,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <f>ÍNDICE(A2:A6; 3) pega o 3º elemento (na planilha a contagem começa em 1).</f>
-        <v/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>=ÍNDICE(A2:A6; 3) pega o 3º elemento (na planilha a contagem começa em 1).</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -550,7 +551,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Para abrir no Google Planilhas: Google Drive → Novo → Upload de arquivo; depois clique no arquivo → Abrir com → Planilhas Google.</t>
+          <t>Esta é a sua cópia: altere à vontade.</t>
         </is>
       </c>
     </row>
